--- a/docs/asset-management/PromptCraft_Voice_Recording_Tracker.xlsx
+++ b/docs/asset-management/PromptCraft_Voice_Recording_Tracker.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R9d4db76357b8496b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recording Queue" sheetId="2" r:id="R3f4900b60a77459f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Decision" sheetId="3" r:id="R19c3d7b9a01b472e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retired - Do Not Record" sheetId="4" r:id="Raab6f61e738d4c8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R192d2ed5b8064b86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recording Queue" sheetId="2" r:id="R5bbf0d93c64249d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Decision" sheetId="3" r:id="R3656174da7144179"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retired - Do Not Record" sheetId="4" r:id="Rea71be5962384e1d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -492,7 +492,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="8" t="str">
-        <x:v>Verified against the active V429 dialogue source · dialogue asset 149 · Phase 6 / patch 527 · current roadmap labels with legacy recording filenames preserved</x:v>
+        <x:v>Verified against active V429 dialogue source · dialogue asset 149 · Dialogue draft through patch 534 · legacy recording filenames preserved</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
@@ -513,13 +513,11 @@
       </x:c>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
-      <x:c r="A5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ready lines</x:t>
-        </x:is>
+      <x:c r="A5" t="str">
+        <x:v>Ready lines</x:v>
       </x:c>
       <x:c r="B5" t="n">
-        <x:v>68</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D5" s="2" t="inlineStr">
         <x:is>
@@ -533,13 +531,11 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
-      <x:c r="A6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Professor Pixel</x:t>
-        </x:is>
+      <x:c r="A6" t="str">
+        <x:v>Professor Pixel ready lines</x:v>
       </x:c>
       <x:c r="B6" t="n">
-        <x:v>43</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D6" s="2" t="inlineStr">
         <x:is>
@@ -553,13 +549,11 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
-      <x:c r="A7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Jordan</x:t>
-        </x:is>
+      <x:c r="A7" t="str">
+        <x:v>Jordan ready lines</x:v>
       </x:c>
       <x:c r="B7" t="n">
-        <x:v>7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="2" t="inlineStr">
         <x:is>
@@ -573,10 +567,8 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="15" customHeight="1">
-      <x:c r="A8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Commercial-model names</x:t>
-        </x:is>
+      <x:c r="A8" t="str">
+        <x:v>Commercial-model names</x:v>
       </x:c>
       <x:c r="B8" t="n">
         <x:v>0</x:v>
@@ -593,10 +585,8 @@
       </x:c>
     </x:row>
     <x:row r="9" ht="15" customHeight="1">
-      <x:c r="A9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Eli</x:t>
-        </x:is>
+      <x:c r="A9" t="str">
+        <x:v>Eli ready lines</x:v>
       </x:c>
       <x:c r="B9" t="n">
         <x:v>18</x:v>
@@ -604,7 +594,14 @@
       <x:c r="D9" s="2" t="n"/>
       <x:c r="E9" s="10" t="n"/>
     </x:row>
-    <x:row r="10" ht="15" customHeight="1"/>
+    <x:row r="10" ht="15" customHeight="1">
+      <x:c r="A10" t="str">
+        <x:v>Scenario 3 draft lines</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="inlineStr">
         <x:is>
@@ -614,7 +611,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="12" t="str">
-        <x:v>Retired the old S1: Engagement queue and retained it only on the retired sheet. The active queue contains 43 Professor Pixel lines, 18 Eli lines for S1: The Content Avalanche, and 7 Jordan lines for S3: The Confident Student Problem. Scenario-02 and s2 filename tokens remain only for source and saved-data compatibility. Current S2: Access Is Part of the Design is still a development shell and has no recording queue.</x:v>
+        <x:v>The active queue contains 54 lines that are ready to record and 14 revised Scenario 3 lines marked Draft, Do Not Record. Scenario 3 now references the planned Week 4 Canvas module, 84% quiz result, practice check, feedback, and reflection activity. Scenario-02 and s2 filename tokens remain only for source and saved-data compatibility. Current S2: Access Is Part of the Design remains a development shell and has no recording queue.</x:v>
       </x:c>
     </x:row>
     <x:row r="13"/>
@@ -2450,7 +2447,7 @@
         <x:v>neutral</x:v>
       </x:c>
       <x:c r="F56" s="5" t="str">
-        <x:v>Meet Jordan. He completes his assignments, earns passing grades, and seems to be doing fine.</x:v>
+        <x:v>Meet Jordan. He finished the Week 4 Canvas module and earned 84% on the module quiz. From the gradebook, everything looks fine.</x:v>
       </x:c>
       <x:c r="G56" s="5" t="str">
         <x:v>p86.mp3</x:v>
@@ -2459,7 +2456,7 @@
         <x:v>assets/audio/voice/professor-pixel/scenario-02/p86.mp3</x:v>
       </x:c>
       <x:c r="I56" s="5" t="str">
-        <x:v>Ready to Record</x:v>
+        <x:v>Draft, Do Not Record</x:v>
       </x:c>
       <x:c r="J56" s="5" t="str">
         <x:v>High</x:v>
@@ -2482,7 +2479,7 @@
         <x:v>thinking</x:v>
       </x:c>
       <x:c r="F57" s="5" t="str">
-        <x:v>His performance improved. His strategy might have worked. But listen carefully to what Jordan actually knows about his learning.</x:v>
+        <x:v>The module shows what Jordan opened and what he scored. It does not show which strategy changed his understanding or where that understanding still breaks down.</x:v>
       </x:c>
       <x:c r="G57" s="5" t="str">
         <x:v>p88.mp3</x:v>
@@ -2491,7 +2488,7 @@
         <x:v>assets/audio/voice/professor-pixel/scenario-02/p88.mp3</x:v>
       </x:c>
       <x:c r="I57" s="5" t="str">
-        <x:v>Ready to Record</x:v>
+        <x:v>Draft, Do Not Record</x:v>
       </x:c>
       <x:c r="J57" s="5" t="str">
         <x:v>High</x:v>
@@ -2514,7 +2511,7 @@
         <x:v>encouraging</x:v>
       </x:c>
       <x:c r="F58" s="5" t="str">
-        <x:v>Let's figure out what's missing.</x:v>
+        <x:v>Inspect the Canvas path and find the missing link between Jordan's strategy, the quiz result, and his next decision.</x:v>
       </x:c>
       <x:c r="G58" s="5" t="str">
         <x:v>p89.mp3</x:v>
@@ -2523,7 +2520,7 @@
         <x:v>assets/audio/voice/professor-pixel/scenario-02/p89.mp3</x:v>
       </x:c>
       <x:c r="I58" s="5" t="str">
-        <x:v>Ready to Record</x:v>
+        <x:v>Draft, Do Not Record</x:v>
       </x:c>
       <x:c r="J58" s="5" t="str">
         <x:v>High</x:v>
@@ -2546,7 +2543,7 @@
         <x:v>proud</x:v>
       </x:c>
       <x:c r="F59" s="5" t="str">
-        <x:v>That's the hidden problem. Jordan has an outcome and a strategy, but no evidence connecting the two. He cannot judge what helped or use that judgment to make his next decision.</x:v>
+        <x:v>That's the hidden problem. Canvas shows Jordan's module activity and grade, but not evidence connecting his study strategy to what he actually understood. He cannot make an informed next decision yet.</x:v>
       </x:c>
       <x:c r="G59" s="5" t="str">
         <x:v>p90.mp3</x:v>
@@ -2555,7 +2552,7 @@
         <x:v>assets/audio/voice/professor-pixel/scenario-02/p90.mp3</x:v>
       </x:c>
       <x:c r="I59" s="5" t="str">
-        <x:v>Ready to Record</x:v>
+        <x:v>Draft, Do Not Record</x:v>
       </x:c>
       <x:c r="J59" s="5" t="str">
         <x:v>High</x:v>
@@ -2578,7 +2575,7 @@
         <x:v>thinking</x:v>
       </x:c>
       <x:c r="F60" s="5" t="str">
-        <x:v>Rereading may not be his best strategy, but replacing it does not solve the deeper problem. Jordan still needs a way to tell why a strategy worked or failed.</x:v>
+        <x:v>Rereading may not be his best strategy, but replacing it inside the next Canvas module does not solve the deeper problem. Jordan still needs evidence showing why a strategy worked or failed.</x:v>
       </x:c>
       <x:c r="G60" s="5" t="str">
         <x:v>p91.mp3</x:v>
@@ -2587,7 +2584,7 @@
         <x:v>assets/audio/voice/professor-pixel/scenario-02/p91.mp3</x:v>
       </x:c>
       <x:c r="I60" s="5" t="str">
-        <x:v>Ready to Record</x:v>
+        <x:v>Draft, Do Not Record</x:v>
       </x:c>
       <x:c r="J60" s="5" t="str">
         <x:v>High</x:v>
@@ -2610,7 +2607,7 @@
         <x:v>skeptical</x:v>
       </x:c>
       <x:c r="F61" s="5" t="str">
-        <x:v>Jordan completed the work and is trying to understand the result. The evidence points somewhere other than motivation.</x:v>
+        <x:v>Jordan completed the Canvas module and is trying to understand the result. The evidence points to a missing learning check, not a motivation problem.</x:v>
       </x:c>
       <x:c r="G61" s="5" t="str">
         <x:v>p92.mp3</x:v>
@@ -2619,7 +2616,7 @@
         <x:v>assets/audio/voice/professor-pixel/scenario-02/p92.mp3</x:v>
       </x:c>
       <x:c r="I61" s="5" t="str">
-        <x:v>Ready to Record</x:v>
+        <x:v>Draft, Do Not Record</x:v>
       </x:c>
       <x:c r="J61" s="5" t="str">
         <x:v>High</x:v>
@@ -2642,7 +2639,7 @@
         <x:v>neutral</x:v>
       </x:c>
       <x:c r="F62" s="5" t="str">
-        <x:v>The grade tells us how Jordan performed. It does not tell Jordan what produced the learning or what he should do next.</x:v>
+        <x:v>The Canvas grade already tells us how Jordan performed. A higher score still does not tell him what produced the learning or what he should do next.</x:v>
       </x:c>
       <x:c r="G62" s="5" t="str">
         <x:v>p93.mp3</x:v>
@@ -2651,7 +2648,7 @@
         <x:v>assets/audio/voice/professor-pixel/scenario-02/p93.mp3</x:v>
       </x:c>
       <x:c r="I62" s="5" t="str">
-        <x:v>Ready to Record</x:v>
+        <x:v>Draft, Do Not Record</x:v>
       </x:c>
       <x:c r="J62" s="5" t="str">
         <x:v>High</x:v>
@@ -2674,7 +2671,7 @@
         <x:v>neutral</x:v>
       </x:c>
       <x:c r="F63" s="5" t="str">
-        <x:v>I got an 84 on this assignment. That's better than last time, so I guess something worked.</x:v>
+        <x:v>Canvas shows my score improved, but I don't know why. I got an 84% on the module quiz after getting 76% last time.</x:v>
       </x:c>
       <x:c r="G63" s="5" t="str">
         <x:v>jordan-s2-01.mp3</x:v>
@@ -2683,7 +2680,7 @@
         <x:v>assets/audio/voice/students/jordan/scenario-02/jordan-s2-01.mp3</x:v>
       </x:c>
       <x:c r="I63" s="5" t="str">
-        <x:v>Ready to Record</x:v>
+        <x:v>Draft, Do Not Record</x:v>
       </x:c>
       <x:c r="J63" s="5" t="str">
         <x:v>High</x:v>
@@ -2706,7 +2703,7 @@
         <x:v>uncertain</x:v>
       </x:c>
       <x:c r="F64" s="5" t="str">
-        <x:v>I reread the chapter a few times. Some parts eventually made more sense, but I couldn't tell you what actually helped.</x:v>
+        <x:v>I reread the module page three times before the quiz. Some parts felt familiar, but I still couldn't explain the difference between the two concepts without my notes.</x:v>
       </x:c>
       <x:c r="G64" s="5" t="str">
         <x:v>jordan-s2-02.mp3</x:v>
@@ -2715,7 +2712,7 @@
         <x:v>assets/audio/voice/students/jordan/scenario-02/jordan-s2-02.mp3</x:v>
       </x:c>
       <x:c r="I64" s="5" t="str">
-        <x:v>Ready to Record</x:v>
+        <x:v>Draft, Do Not Record</x:v>
       </x:c>
       <x:c r="J64" s="5" t="str">
         <x:v>High</x:v>
@@ -2738,7 +2735,7 @@
         <x:v>frustrated</x:v>
       </x:c>
       <x:c r="F65" s="5" t="str">
-        <x:v>Next time I'll probably reread everything again and hope it works.</x:v>
+        <x:v>The next module opens Monday. I'll probably reread everything again and hope the score keeps improving.</x:v>
       </x:c>
       <x:c r="G65" s="5" t="str">
         <x:v>jordan-s2-03.mp3</x:v>
@@ -2747,7 +2744,7 @@
         <x:v>assets/audio/voice/students/jordan/scenario-02/jordan-s2-03.mp3</x:v>
       </x:c>
       <x:c r="I65" s="5" t="str">
-        <x:v>Ready to Record</x:v>
+        <x:v>Draft, Do Not Record</x:v>
       </x:c>
       <x:c r="J65" s="5" t="str">
         <x:v>High</x:v>
@@ -2770,7 +2767,7 @@
         <x:v>confident</x:v>
       </x:c>
       <x:c r="F66" s="5" t="str">
-        <x:v>I’d say I’m a four out of five. I feel better about it this time.</x:v>
+        <x:v>In the Canvas reflection, I’d rate my confidence four out of five. I feel better, but I still can't explain what the rereading changed.</x:v>
       </x:c>
       <x:c r="G66" s="5" t="str">
         <x:v>jordan-s2-intervention-confidence.mp3</x:v>
@@ -2779,7 +2776,7 @@
         <x:v>assets/audio/voice/students/jordan/scenario-02/jordan-s2-intervention-confidence.mp3</x:v>
       </x:c>
       <x:c r="I66" s="5" t="str">
-        <x:v>Ready to Record</x:v>
+        <x:v>Draft, Do Not Record</x:v>
       </x:c>
       <x:c r="J66" s="5" t="str">
         <x:v>High</x:v>
@@ -2802,7 +2799,7 @@
         <x:v>thinking</x:v>
       </x:c>
       <x:c r="F67" s="5" t="str">
-        <x:v>I reread the chapter three times and highlighted the parts that seemed important.</x:v>
+        <x:v>I reread the module page three times and highlighted the parts that seemed important.</x:v>
       </x:c>
       <x:c r="G67" s="5" t="str">
         <x:v>jordan-s2-intervention-strategy.mp3</x:v>
@@ -2811,7 +2808,7 @@
         <x:v>assets/audio/voice/students/jordan/scenario-02/jordan-s2-intervention-strategy.mp3</x:v>
       </x:c>
       <x:c r="I67" s="5" t="str">
-        <x:v>Ready to Record</x:v>
+        <x:v>Draft, Do Not Record</x:v>
       </x:c>
       <x:c r="J67" s="5" t="str">
         <x:v>High</x:v>
@@ -2834,7 +2831,7 @@
         <x:v>confident</x:v>
       </x:c>
       <x:c r="F68" s="5" t="str">
-        <x:v>I got an 84 instead of a 76, so rereading must have worked.</x:v>
+        <x:v>My Canvas grade went from 76% to 84%, so rereading must have worked.</x:v>
       </x:c>
       <x:c r="G68" s="5" t="str">
         <x:v>jordan-s2-intervention-grade.mp3</x:v>
@@ -2843,7 +2840,7 @@
         <x:v>assets/audio/voice/students/jordan/scenario-02/jordan-s2-intervention-grade.mp3</x:v>
       </x:c>
       <x:c r="I68" s="5" t="str">
-        <x:v>Ready to Record</x:v>
+        <x:v>Draft, Do Not Record</x:v>
       </x:c>
       <x:c r="J68" s="5" t="str">
         <x:v>High</x:v>
@@ -2866,7 +2863,7 @@
         <x:v>thinking</x:v>
       </x:c>
       <x:c r="F69" s="5" t="str">
-        <x:v>I could define both concepts, but without my notes I still couldn’t explain the difference. Rereading helped me recognize them, but it didn’t help me compare them. I need to try examples next.</x:v>
+        <x:v>On the Canvas practice check, I could define both concepts, but without my notes I still couldn’t explain the difference. Rereading helped me recognize them, but it didn’t help me compare them. I need to try examples next.</x:v>
       </x:c>
       <x:c r="G69" s="5" t="str">
         <x:v>jordan-s2-intervention-evidence.mp3</x:v>
@@ -2875,7 +2872,7 @@
         <x:v>assets/audio/voice/students/jordan/scenario-02/jordan-s2-intervention-evidence.mp3</x:v>
       </x:c>
       <x:c r="I69" s="5" t="str">
-        <x:v>Ready to Record</x:v>
+        <x:v>Draft, Do Not Record</x:v>
       </x:c>
       <x:c r="J69" s="5" t="str">
         <x:v>High</x:v>
@@ -2889,7 +2886,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb07dfc2224a54914"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4dd1a4efc35e4c2a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3064,7 +3061,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1ddbb4b171c4ec6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cce150aefae4896"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3272,7 +3269,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0f07bfe831a4169"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf5c945c3c4d4938"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/asset-management/PromptCraft_Voice_Recording_Tracker.xlsx
+++ b/docs/asset-management/PromptCraft_Voice_Recording_Tracker.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R192d2ed5b8064b86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recording Queue" sheetId="2" r:id="R5bbf0d93c64249d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Decision" sheetId="3" r:id="R3656174da7144179"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retired - Do Not Record" sheetId="4" r:id="Rea71be5962384e1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R4cd5137ce34c4ade"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recording Queue" sheetId="2" r:id="R4660280d0fd74b36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Decision" sheetId="3" r:id="R940a18694c934ba9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retired - Do Not Record" sheetId="4" r:id="R4c9ca394fcaf4519"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -492,7 +492,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="8" t="str">
-        <x:v>Verified against active V429 dialogue source · dialogue asset 149 · Dialogue draft through patch 534 · legacy recording filenames preserved</x:v>
+        <x:v>Verified against active V429 dialogue source · dialogue asset 149 · Dialogue draft through patch 535 · legacy recording filenames preserved</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
@@ -596,10 +596,10 @@
     </x:row>
     <x:row r="10" ht="15" customHeight="1">
       <x:c r="A10" t="str">
-        <x:v>Scenario 3 draft lines</x:v>
+        <x:v>Scenario draft lines</x:v>
       </x:c>
       <x:c r="B10" t="n">
-        <x:v>14</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -611,7 +611,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="12" t="str">
-        <x:v>The active queue contains 54 lines that are ready to record and 14 revised Scenario 3 lines marked Draft, Do Not Record. Scenario 3 now references the planned Week 4 Canvas module, 84% quiz result, practice check, feedback, and reflection activity. Scenario-02 and s2 filename tokens remain only for source and saved-data compatibility. Current S2: Access Is Part of the Design remains a development shell and has no recording queue.</x:v>
+        <x:v>The active queue contains 54 lines that are ready to record and 50 revised scenario lines marked Draft, Do Not Record. Scenario 3 draft lines: 14. Scenario 4 draft lines: 36. The Scenario 3 dialogue draft through patch 534 remains unchanged. Scenario 4 now references the planned Week 4 Canvas quiz, 96% result, county planning assignment, submission evidence, rubric, and changed-constraint revision. Internal scenario-03 and s3 path tokens remain only for source and saved-data compatibility.</x:v>
       </x:c>
     </x:row>
     <x:row r="13"/>
@@ -2878,6 +2878,1158 @@
         <x:v>High</x:v>
       </x:c>
     </x:row>
+    <x:row r="70">
+      <x:c r="A70" t="str">
+        <x:v>Professor Pixel</x:v>
+      </x:c>
+      <x:c r="B70" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C70" t="str">
+        <x:v>Opening</x:v>
+      </x:c>
+      <x:c r="D70" t="str">
+        <x:v>p-s3-01</x:v>
+      </x:c>
+      <x:c r="E70" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="F70" t="str">
+        <x:v>Maya earned 96% on the Week 4 Canvas quiz. The gradebook suggests mastery, but the course outcome asks for more than the quiz required.</x:v>
+      </x:c>
+      <x:c r="G70" t="str">
+        <x:v>p-s3-01.mp3</x:v>
+      </x:c>
+      <x:c r="H70" t="str">
+        <x:v>assets/audio/voice/professor-pixel/scenario-03/p-s3-01.mp3</x:v>
+      </x:c>
+      <x:c r="I70" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J70" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" t="str">
+        <x:v>Maya</x:v>
+      </x:c>
+      <x:c r="B71" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C71" t="str">
+        <x:v>Opening</x:v>
+      </x:c>
+      <x:c r="D71" t="str">
+        <x:v>maya-s3-01</x:v>
+      </x:c>
+      <x:c r="E71" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="F71" t="str">
+        <x:v>Canvas says I did really well. I knew almost every answer, and the feedback confirmed the terms I missed.</x:v>
+      </x:c>
+      <x:c r="G71" t="str">
+        <x:v>maya-s3-01.mp3</x:v>
+      </x:c>
+      <x:c r="H71" t="str">
+        <x:v>assets/audio/voice/students/maya/scenario-03/maya-s3-01.mp3</x:v>
+      </x:c>
+      <x:c r="I71" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J71" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" t="str">
+        <x:v>Maya</x:v>
+      </x:c>
+      <x:c r="B72" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C72" t="str">
+        <x:v>Opening</x:v>
+      </x:c>
+      <x:c r="D72" t="str">
+        <x:v>maya-s3-02</x:v>
+      </x:c>
+      <x:c r="E72" t="str">
+        <x:v>uncertain</x:v>
+      </x:c>
+      <x:c r="F72" t="str">
+        <x:v>But when I opened the Canvas Assignment and saw the county planning brief, I did not know how to turn those terms into a recommendation.</x:v>
+      </x:c>
+      <x:c r="G72" t="str">
+        <x:v>maya-s3-02.mp3</x:v>
+      </x:c>
+      <x:c r="H72" t="str">
+        <x:v>assets/audio/voice/students/maya/scenario-03/maya-s3-02.mp3</x:v>
+      </x:c>
+      <x:c r="I72" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J72" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" t="str">
+        <x:v>Professor Pixel</x:v>
+      </x:c>
+      <x:c r="B73" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C73" t="str">
+        <x:v>Opening</x:v>
+      </x:c>
+      <x:c r="D73" t="str">
+        <x:v>p-s3-02</x:v>
+      </x:c>
+      <x:c r="E73" t="str">
+        <x:v>thinking</x:v>
+      </x:c>
+      <x:c r="F73" t="str">
+        <x:v>That gap is the case. The quiz score is accurate for the questions asked, but it may not support the larger claim about Maya's planning judgment.</x:v>
+      </x:c>
+      <x:c r="G73" t="str">
+        <x:v>p-s3-02.mp3</x:v>
+      </x:c>
+      <x:c r="H73" t="str">
+        <x:v>assets/audio/voice/professor-pixel/scenario-03/p-s3-02.mp3</x:v>
+      </x:c>
+      <x:c r="I73" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J73" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" t="str">
+        <x:v>Maya</x:v>
+      </x:c>
+      <x:c r="B74" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C74" t="str">
+        <x:v>Opening</x:v>
+      </x:c>
+      <x:c r="D74" t="str">
+        <x:v>maya-s3-03</x:v>
+      </x:c>
+      <x:c r="E74" t="str">
+        <x:v>thinking</x:v>
+      </x:c>
+      <x:c r="F74" t="str">
+        <x:v>The quiz asked me to define terms, order the planning cycle, and choose an answer in one short example.</x:v>
+      </x:c>
+      <x:c r="G74" t="str">
+        <x:v>maya-s3-03.mp3</x:v>
+      </x:c>
+      <x:c r="H74" t="str">
+        <x:v>assets/audio/voice/students/maya/scenario-03/maya-s3-03.mp3</x:v>
+      </x:c>
+      <x:c r="I74" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J74" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" t="str">
+        <x:v>Professor Pixel</x:v>
+      </x:c>
+      <x:c r="B75" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C75" t="str">
+        <x:v>Opening</x:v>
+      </x:c>
+      <x:c r="D75" t="str">
+        <x:v>p-s3-03</x:v>
+      </x:c>
+      <x:c r="E75" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="F75" t="str">
+        <x:v>The module outcome asks you to analyze a rural planning problem, recommend a feasible response, and justify the trade-offs.</x:v>
+      </x:c>
+      <x:c r="G75" t="str">
+        <x:v>p-s3-03.mp3</x:v>
+      </x:c>
+      <x:c r="H75" t="str">
+        <x:v>assets/audio/voice/professor-pixel/scenario-03/p-s3-03.mp3</x:v>
+      </x:c>
+      <x:c r="I75" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J75" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" t="str">
+        <x:v>Maya</x:v>
+      </x:c>
+      <x:c r="B76" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C76" t="str">
+        <x:v>Opening</x:v>
+      </x:c>
+      <x:c r="D76" t="str">
+        <x:v>maya-s3-04</x:v>
+      </x:c>
+      <x:c r="E76" t="str">
+        <x:v>frustrated</x:v>
+      </x:c>
+      <x:c r="F76" t="str">
+        <x:v>The gradebook shows 96%, but I never had to produce that kind of decision.</x:v>
+      </x:c>
+      <x:c r="G76" t="str">
+        <x:v>maya-s3-04.mp3</x:v>
+      </x:c>
+      <x:c r="H76" t="str">
+        <x:v>assets/audio/voice/students/maya/scenario-03/maya-s3-04.mp3</x:v>
+      </x:c>
+      <x:c r="I76" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" t="str">
+        <x:v>Professor Pixel</x:v>
+      </x:c>
+      <x:c r="B77" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C77" t="str">
+        <x:v>Opening</x:v>
+      </x:c>
+      <x:c r="D77" t="str">
+        <x:v>p-s3-04</x:v>
+      </x:c>
+      <x:c r="E77" t="str">
+        <x:v>encouraging</x:v>
+      </x:c>
+      <x:c r="F77" t="str">
+        <x:v>Then let's map what the Canvas quiz makes visible and what the assignment still needs to collect.</x:v>
+      </x:c>
+      <x:c r="G77" t="str">
+        <x:v>p-s3-04.mp3</x:v>
+      </x:c>
+      <x:c r="H77" t="str">
+        <x:v>assets/audio/voice/professor-pixel/scenario-03/p-s3-04.mp3</x:v>
+      </x:c>
+      <x:c r="I77" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J77" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" t="str">
+        <x:v>Maya</x:v>
+      </x:c>
+      <x:c r="B78" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C78" t="str">
+        <x:v>Diagnosis review</x:v>
+      </x:c>
+      <x:c r="D78" t="str">
+        <x:v>maya-s3-05</x:v>
+      </x:c>
+      <x:c r="E78" t="str">
+        <x:v>thinking</x:v>
+      </x:c>
+      <x:c r="F78" t="str">
+        <x:v>Now I see why studying the quiz worked. Canvas showed me which definitions and examples to review.</x:v>
+      </x:c>
+      <x:c r="G78" t="str">
+        <x:v>maya-s3-05.mp3</x:v>
+      </x:c>
+      <x:c r="H78" t="str">
+        <x:v>assets/audio/voice/students/maya/scenario-03/maya-s3-05.mp3</x:v>
+      </x:c>
+      <x:c r="I78" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J78" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" t="str">
+        <x:v>Professor Pixel</x:v>
+      </x:c>
+      <x:c r="B79" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C79" t="str">
+        <x:v>Diagnosis review</x:v>
+      </x:c>
+      <x:c r="D79" t="str">
+        <x:v>p-s3-05</x:v>
+      </x:c>
+      <x:c r="E79" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="F79" t="str">
+        <x:v>That feedback was useful. It supported knowledge and explanation, but not the full decision-making outcome.</x:v>
+      </x:c>
+      <x:c r="G79" t="str">
+        <x:v>p-s3-05.mp3</x:v>
+      </x:c>
+      <x:c r="H79" t="str">
+        <x:v>assets/audio/voice/professor-pixel/scenario-03/p-s3-05.mp3</x:v>
+      </x:c>
+      <x:c r="I79" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J79" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" t="str">
+        <x:v>Maya</x:v>
+      </x:c>
+      <x:c r="B80" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C80" t="str">
+        <x:v>Diagnosis review</x:v>
+      </x:c>
+      <x:c r="D80" t="str">
+        <x:v>maya-s3-06</x:v>
+      </x:c>
+      <x:c r="E80" t="str">
+        <x:v>uncertain</x:v>
+      </x:c>
+      <x:c r="F80" t="str">
+        <x:v>So the 96% is real evidence, just not evidence that I can complete the Canvas Assignment.</x:v>
+      </x:c>
+      <x:c r="G80" t="str">
+        <x:v>maya-s3-06.mp3</x:v>
+      </x:c>
+      <x:c r="H80" t="str">
+        <x:v>assets/audio/voice/students/maya/scenario-03/maya-s3-06.mp3</x:v>
+      </x:c>
+      <x:c r="I80" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J80" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" t="str">
+        <x:v>Professor Pixel</x:v>
+      </x:c>
+      <x:c r="B81" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C81" t="str">
+        <x:v>Diagnosis review</x:v>
+      </x:c>
+      <x:c r="D81" t="str">
+        <x:v>p-s3-06</x:v>
+      </x:c>
+      <x:c r="E81" t="str">
+        <x:v>encouraging</x:v>
+      </x:c>
+      <x:c r="F81" t="str">
+        <x:v>Exactly. Now design the assignment, submission, and rubric so the intended performance becomes visible.</x:v>
+      </x:c>
+      <x:c r="G81" t="str">
+        <x:v>p-s3-06.mp3</x:v>
+      </x:c>
+      <x:c r="H81" t="str">
+        <x:v>assets/audio/voice/professor-pixel/scenario-03/p-s3-06.mp3</x:v>
+      </x:c>
+      <x:c r="I81" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J81" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" t="str">
+        <x:v>Maya</x:v>
+      </x:c>
+      <x:c r="B82" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C82" t="str">
+        <x:v>Blueprint: strong</x:v>
+      </x:c>
+      <x:c r="D82" t="str">
+        <x:v>maya-s3-07a</x:v>
+      </x:c>
+      <x:c r="E82" t="str">
+        <x:v>confident</x:v>
+      </x:c>
+      <x:c r="F82" t="str">
+        <x:v>The Canvas Assignment now gives me a county brief, asks for a recommendation, and requires evidence and trade-offs in the same submission.</x:v>
+      </x:c>
+      <x:c r="G82" t="str">
+        <x:v>maya-s3-07a.mp3</x:v>
+      </x:c>
+      <x:c r="H82" t="str">
+        <x:v>assets/audio/voice/students/maya/scenario-03/maya-s3-07a.mp3</x:v>
+      </x:c>
+      <x:c r="I82" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J82" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" t="str">
+        <x:v>Professor Pixel</x:v>
+      </x:c>
+      <x:c r="B83" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C83" t="str">
+        <x:v>Blueprint: strong</x:v>
+      </x:c>
+      <x:c r="D83" t="str">
+        <x:v>p-s3-07a</x:v>
+      </x:c>
+      <x:c r="E83" t="str">
+        <x:v>thinking</x:v>
+      </x:c>
+      <x:c r="F83" t="str">
+        <x:v>Strong alignment. But a well-designed assignment can still invite a claim larger than one submission supports.</x:v>
+      </x:c>
+      <x:c r="G83" t="str">
+        <x:v>p-s3-07a.mp3</x:v>
+      </x:c>
+      <x:c r="H83" t="str">
+        <x:v>assets/audio/voice/professor-pixel/scenario-03/p-s3-07a.mp3</x:v>
+      </x:c>
+      <x:c r="I83" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J83" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" t="str">
+        <x:v>Maya</x:v>
+      </x:c>
+      <x:c r="B84" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C84" t="str">
+        <x:v>Blueprint: strong</x:v>
+      </x:c>
+      <x:c r="D84" t="str">
+        <x:v>maya-s3-08a</x:v>
+      </x:c>
+      <x:c r="E84" t="str">
+        <x:v>thinking</x:v>
+      </x:c>
+      <x:c r="F84" t="str">
+        <x:v>Then we should test which parts of the Canvas submission actually demonstrate the outcome.</x:v>
+      </x:c>
+      <x:c r="G84" t="str">
+        <x:v>maya-s3-08a.mp3</x:v>
+      </x:c>
+      <x:c r="H84" t="str">
+        <x:v>assets/audio/voice/students/maya/scenario-03/maya-s3-08a.mp3</x:v>
+      </x:c>
+      <x:c r="I84" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J84" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" t="str">
+        <x:v>Professor Pixel</x:v>
+      </x:c>
+      <x:c r="B85" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C85" t="str">
+        <x:v>Blueprint: strong</x:v>
+      </x:c>
+      <x:c r="D85" t="str">
+        <x:v>p-s3-08a</x:v>
+      </x:c>
+      <x:c r="E85" t="str">
+        <x:v>proud</x:v>
+      </x:c>
+      <x:c r="F85" t="str">
+        <x:v>Exactly. Stress-test the evidence.</x:v>
+      </x:c>
+      <x:c r="G85" t="str">
+        <x:v>p-s3-08a.mp3</x:v>
+      </x:c>
+      <x:c r="H85" t="str">
+        <x:v>assets/audio/voice/professor-pixel/scenario-03/p-s3-08a.mp3</x:v>
+      </x:c>
+      <x:c r="I85" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J85" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" t="str">
+        <x:v>Maya</x:v>
+      </x:c>
+      <x:c r="B86" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C86" t="str">
+        <x:v>Blueprint: mixed</x:v>
+      </x:c>
+      <x:c r="D86" t="str">
+        <x:v>maya-s3-07b</x:v>
+      </x:c>
+      <x:c r="E86" t="str">
+        <x:v>thinking</x:v>
+      </x:c>
+      <x:c r="F86" t="str">
+        <x:v>The Canvas Assignment feels more realistic, but I could still submit a recommendation without showing enough of my reasoning.</x:v>
+      </x:c>
+      <x:c r="G86" t="str">
+        <x:v>maya-s3-07b.mp3</x:v>
+      </x:c>
+      <x:c r="H86" t="str">
+        <x:v>assets/audio/voice/students/maya/scenario-03/maya-s3-07b.mp3</x:v>
+      </x:c>
+      <x:c r="I86" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J86" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" t="str">
+        <x:v>Professor Pixel</x:v>
+      </x:c>
+      <x:c r="B87" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C87" t="str">
+        <x:v>Blueprint: mixed</x:v>
+      </x:c>
+      <x:c r="D87" t="str">
+        <x:v>p-s3-07b</x:v>
+      </x:c>
+      <x:c r="E87" t="str">
+        <x:v>thinking</x:v>
+      </x:c>
+      <x:c r="F87" t="str">
+        <x:v>That is the right concern. A Canvas task can look authentic while the submission and rubric still collect weak evidence.</x:v>
+      </x:c>
+      <x:c r="G87" t="str">
+        <x:v>p-s3-07b.mp3</x:v>
+      </x:c>
+      <x:c r="H87" t="str">
+        <x:v>assets/audio/voice/professor-pixel/scenario-03/p-s3-07b.mp3</x:v>
+      </x:c>
+      <x:c r="I87" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J87" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" t="str">
+        <x:v>Maya</x:v>
+      </x:c>
+      <x:c r="B88" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C88" t="str">
+        <x:v>Blueprint: mixed</x:v>
+      </x:c>
+      <x:c r="D88" t="str">
+        <x:v>maya-s3-08b</x:v>
+      </x:c>
+      <x:c r="E88" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="F88" t="str">
+        <x:v>Then let's see which parts of the submission support the outcome and which only make it look complete.</x:v>
+      </x:c>
+      <x:c r="G88" t="str">
+        <x:v>maya-s3-08b.mp3</x:v>
+      </x:c>
+      <x:c r="H88" t="str">
+        <x:v>assets/audio/voice/students/maya/scenario-03/maya-s3-08b.mp3</x:v>
+      </x:c>
+      <x:c r="I88" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J88" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" t="str">
+        <x:v>Professor Pixel</x:v>
+      </x:c>
+      <x:c r="B89" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C89" t="str">
+        <x:v>Blueprint: mixed</x:v>
+      </x:c>
+      <x:c r="D89" t="str">
+        <x:v>p-s3-08b</x:v>
+      </x:c>
+      <x:c r="E89" t="str">
+        <x:v>encouraging</x:v>
+      </x:c>
+      <x:c r="F89" t="str">
+        <x:v>Stress-test the evidence.</x:v>
+      </x:c>
+      <x:c r="G89" t="str">
+        <x:v>p-s3-08b.mp3</x:v>
+      </x:c>
+      <x:c r="H89" t="str">
+        <x:v>assets/audio/voice/professor-pixel/scenario-03/p-s3-08b.mp3</x:v>
+      </x:c>
+      <x:c r="I89" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J89" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" t="str">
+        <x:v>Maya</x:v>
+      </x:c>
+      <x:c r="B90" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C90" t="str">
+        <x:v>Blueprint: weak</x:v>
+      </x:c>
+      <x:c r="D90" t="str">
+        <x:v>maya-s3-07c</x:v>
+      </x:c>
+      <x:c r="E90" t="str">
+        <x:v>uncertain</x:v>
+      </x:c>
+      <x:c r="F90" t="str">
+        <x:v>I think I could still study the rubric checklist and complete the Canvas Assignment without making the decision myself.</x:v>
+      </x:c>
+      <x:c r="G90" t="str">
+        <x:v>maya-s3-07c.mp3</x:v>
+      </x:c>
+      <x:c r="H90" t="str">
+        <x:v>assets/audio/voice/students/maya/scenario-03/maya-s3-07c.mp3</x:v>
+      </x:c>
+      <x:c r="I90" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J90" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="str">
+        <x:v>Professor Pixel</x:v>
+      </x:c>
+      <x:c r="B91" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C91" t="str">
+        <x:v>Blueprint: weak</x:v>
+      </x:c>
+      <x:c r="D91" t="str">
+        <x:v>p-s3-07c</x:v>
+      </x:c>
+      <x:c r="E91" t="str">
+        <x:v>skeptical</x:v>
+      </x:c>
+      <x:c r="F91" t="str">
+        <x:v>Then the Canvas shell changed, but the assessment claim did not.</x:v>
+      </x:c>
+      <x:c r="G91" t="str">
+        <x:v>p-s3-07c.mp3</x:v>
+      </x:c>
+      <x:c r="H91" t="str">
+        <x:v>assets/audio/voice/professor-pixel/scenario-03/p-s3-07c.mp3</x:v>
+      </x:c>
+      <x:c r="I91" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J91" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="str">
+        <x:v>Maya</x:v>
+      </x:c>
+      <x:c r="B92" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C92" t="str">
+        <x:v>Blueprint: weak</x:v>
+      </x:c>
+      <x:c r="D92" t="str">
+        <x:v>maya-s3-08c</x:v>
+      </x:c>
+      <x:c r="E92" t="str">
+        <x:v>thinking</x:v>
+      </x:c>
+      <x:c r="F92" t="str">
+        <x:v>The submitted work should reveal that gap quickly.</x:v>
+      </x:c>
+      <x:c r="G92" t="str">
+        <x:v>maya-s3-08c.mp3</x:v>
+      </x:c>
+      <x:c r="H92" t="str">
+        <x:v>assets/audio/voice/students/maya/scenario-03/maya-s3-08c.mp3</x:v>
+      </x:c>
+      <x:c r="I92" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J92" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="str">
+        <x:v>Professor Pixel</x:v>
+      </x:c>
+      <x:c r="B93" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C93" t="str">
+        <x:v>Blueprint: weak</x:v>
+      </x:c>
+      <x:c r="D93" t="str">
+        <x:v>p-s3-08c</x:v>
+      </x:c>
+      <x:c r="E93" t="str">
+        <x:v>encouraging</x:v>
+      </x:c>
+      <x:c r="F93" t="str">
+        <x:v>Exactly. Test what the submission actually proves.</x:v>
+      </x:c>
+      <x:c r="G93" t="str">
+        <x:v>p-s3-08c.mp3</x:v>
+      </x:c>
+      <x:c r="H93" t="str">
+        <x:v>assets/audio/voice/professor-pixel/scenario-03/p-s3-08c.mp3</x:v>
+      </x:c>
+      <x:c r="I93" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J93" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="str">
+        <x:v>Maya</x:v>
+      </x:c>
+      <x:c r="B94" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C94" t="str">
+        <x:v>Evidence stress test</x:v>
+      </x:c>
+      <x:c r="D94" t="str">
+        <x:v>maya-s3-09</x:v>
+      </x:c>
+      <x:c r="E94" t="str">
+        <x:v>thinking</x:v>
+      </x:c>
+      <x:c r="F94" t="str">
+        <x:v>The polished memo and correct vocabulary would score well in Canvas, but neither one shows whether my recommendation fits the county evidence.</x:v>
+      </x:c>
+      <x:c r="G94" t="str">
+        <x:v>maya-s3-09.mp3</x:v>
+      </x:c>
+      <x:c r="H94" t="str">
+        <x:v>assets/audio/voice/students/maya/scenario-03/maya-s3-09.mp3</x:v>
+      </x:c>
+      <x:c r="I94" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J94" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="str">
+        <x:v>Professor Pixel</x:v>
+      </x:c>
+      <x:c r="B95" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C95" t="str">
+        <x:v>Evidence stress test</x:v>
+      </x:c>
+      <x:c r="D95" t="str">
+        <x:v>p-s3-09</x:v>
+      </x:c>
+      <x:c r="E95" t="str">
+        <x:v>thinking</x:v>
+      </x:c>
+      <x:c r="F95" t="str">
+        <x:v>Right. The Canvas submission must expose the performance, not just contain a professional-looking file.</x:v>
+      </x:c>
+      <x:c r="G95" t="str">
+        <x:v>p-s3-09.mp3</x:v>
+      </x:c>
+      <x:c r="H95" t="str">
+        <x:v>assets/audio/voice/professor-pixel/scenario-03/p-s3-09.mp3</x:v>
+      </x:c>
+      <x:c r="I95" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J95" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="str">
+        <x:v>Maya</x:v>
+      </x:c>
+      <x:c r="B96" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C96" t="str">
+        <x:v>Evidence stress test</x:v>
+      </x:c>
+      <x:c r="D96" t="str">
+        <x:v>maya-s3-10</x:v>
+      </x:c>
+      <x:c r="E96" t="str">
+        <x:v>confident</x:v>
+      </x:c>
+      <x:c r="F96" t="str">
+        <x:v>The recommendation, evidence table, rejected alternative, and changed constraint make the planning judgment visible.</x:v>
+      </x:c>
+      <x:c r="G96" t="str">
+        <x:v>maya-s3-10.mp3</x:v>
+      </x:c>
+      <x:c r="H96" t="str">
+        <x:v>assets/audio/voice/students/maya/scenario-03/maya-s3-10.mp3</x:v>
+      </x:c>
+      <x:c r="I96" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J96" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="str">
+        <x:v>Professor Pixel</x:v>
+      </x:c>
+      <x:c r="B97" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C97" t="str">
+        <x:v>Evidence stress test</x:v>
+      </x:c>
+      <x:c r="D97" t="str">
+        <x:v>p-s3-10</x:v>
+      </x:c>
+      <x:c r="E97" t="str">
+        <x:v>encouraging</x:v>
+      </x:c>
+      <x:c r="F97" t="str">
+        <x:v>Now let's give that Canvas evidence to Babbage and audit how far its claim reaches.</x:v>
+      </x:c>
+      <x:c r="G97" t="str">
+        <x:v>p-s3-10.mp3</x:v>
+      </x:c>
+      <x:c r="H97" t="str">
+        <x:v>assets/audio/voice/professor-pixel/scenario-03/p-s3-10.mp3</x:v>
+      </x:c>
+      <x:c r="I97" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J97" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="str">
+        <x:v>Maya</x:v>
+      </x:c>
+      <x:c r="B98" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>Babbage audit</x:v>
+      </x:c>
+      <x:c r="D98" t="str">
+        <x:v>maya-s3-11</x:v>
+      </x:c>
+      <x:c r="E98" t="str">
+        <x:v>uncertain</x:v>
+      </x:c>
+      <x:c r="F98" t="str">
+        <x:v>One strong Canvas submission still does not prove I can transfer the skill to every new planning problem.</x:v>
+      </x:c>
+      <x:c r="G98" t="str">
+        <x:v>maya-s3-11.mp3</x:v>
+      </x:c>
+      <x:c r="H98" t="str">
+        <x:v>assets/audio/voice/students/maya/scenario-03/maya-s3-11.mp3</x:v>
+      </x:c>
+      <x:c r="I98" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J98" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="str">
+        <x:v>Professor Pixel</x:v>
+      </x:c>
+      <x:c r="B99" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>Babbage audit</x:v>
+      </x:c>
+      <x:c r="D99" t="str">
+        <x:v>p-s3-11</x:v>
+      </x:c>
+      <x:c r="E99" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="F99" t="str">
+        <x:v>Right. The submission supports the claim only at the level of the evidence it contains.</x:v>
+      </x:c>
+      <x:c r="G99" t="str">
+        <x:v>p-s3-11.mp3</x:v>
+      </x:c>
+      <x:c r="H99" t="str">
+        <x:v>assets/audio/voice/professor-pixel/scenario-03/p-s3-11.mp3</x:v>
+      </x:c>
+      <x:c r="I99" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J99" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="str">
+        <x:v>Maya</x:v>
+      </x:c>
+      <x:c r="B100" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C100" t="str">
+        <x:v>Babbage audit</x:v>
+      </x:c>
+      <x:c r="D100" t="str">
+        <x:v>maya-s3-12</x:v>
+      </x:c>
+      <x:c r="E100" t="str">
+        <x:v>thinking</x:v>
+      </x:c>
+      <x:c r="F100" t="str">
+        <x:v>If the rubric is supposed to support a transfer claim, the assignment needs to show how I adapt when a meaningful condition changes.</x:v>
+      </x:c>
+      <x:c r="G100" t="str">
+        <x:v>maya-s3-12.mp3</x:v>
+      </x:c>
+      <x:c r="H100" t="str">
+        <x:v>assets/audio/voice/students/maya/scenario-03/maya-s3-12.mp3</x:v>
+      </x:c>
+      <x:c r="I100" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J100" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="str">
+        <x:v>Professor Pixel</x:v>
+      </x:c>
+      <x:c r="B101" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C101" t="str">
+        <x:v>Babbage audit</x:v>
+      </x:c>
+      <x:c r="D101" t="str">
+        <x:v>p-s3-12</x:v>
+      </x:c>
+      <x:c r="E101" t="str">
+        <x:v>encouraging</x:v>
+      </x:c>
+      <x:c r="F101" t="str">
+        <x:v>Exactly. Repair that inference gap without rebuilding the whole Canvas assessment.</x:v>
+      </x:c>
+      <x:c r="G101" t="str">
+        <x:v>p-s3-12.mp3</x:v>
+      </x:c>
+      <x:c r="H101" t="str">
+        <x:v>assets/audio/voice/professor-pixel/scenario-03/p-s3-12.mp3</x:v>
+      </x:c>
+      <x:c r="I101" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J101" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="str">
+        <x:v>Maya</x:v>
+      </x:c>
+      <x:c r="B102" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C102" t="str">
+        <x:v>Final exchange</x:v>
+      </x:c>
+      <x:c r="D102" t="str">
+        <x:v>maya-s3-13</x:v>
+      </x:c>
+      <x:c r="E102" t="str">
+        <x:v>confident</x:v>
+      </x:c>
+      <x:c r="F102" t="str">
+        <x:v>Adding the changed constraint to the Canvas Assignment made me revise the recommendation and explain why my reasoning changed.</x:v>
+      </x:c>
+      <x:c r="G102" t="str">
+        <x:v>maya-s3-13.mp3</x:v>
+      </x:c>
+      <x:c r="H102" t="str">
+        <x:v>assets/audio/voice/students/maya/scenario-03/maya-s3-13.mp3</x:v>
+      </x:c>
+      <x:c r="I102" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J102" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str">
+        <x:v>Professor Pixel</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>Final exchange</x:v>
+      </x:c>
+      <x:c r="D103" t="str">
+        <x:v>p-s3-13</x:v>
+      </x:c>
+      <x:c r="E103" t="str">
+        <x:v>proud</x:v>
+      </x:c>
+      <x:c r="F103" t="str">
+        <x:v>And the submission plus rubric can now show the adaptation, not just the final answer.</x:v>
+      </x:c>
+      <x:c r="G103" t="str">
+        <x:v>p-s3-13.mp3</x:v>
+      </x:c>
+      <x:c r="H103" t="str">
+        <x:v>assets/audio/voice/professor-pixel/scenario-03/p-s3-13.mp3</x:v>
+      </x:c>
+      <x:c r="I103" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J103" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>Maya</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>Final exchange</x:v>
+      </x:c>
+      <x:c r="D104" t="str">
+        <x:v>maya-s3-14</x:v>
+      </x:c>
+      <x:c r="E104" t="str">
+        <x:v>neutral</x:v>
+      </x:c>
+      <x:c r="F104" t="str">
+        <x:v>The 96% still matters, but now Canvas holds evidence that matches more of the module outcome.</x:v>
+      </x:c>
+      <x:c r="G104" t="str">
+        <x:v>maya-s3-14.mp3</x:v>
+      </x:c>
+      <x:c r="H104" t="str">
+        <x:v>assets/audio/voice/students/maya/scenario-03/maya-s3-14.mp3</x:v>
+      </x:c>
+      <x:c r="I104" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J104" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="str">
+        <x:v>Professor Pixel</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>S4: The 96% Problem</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>Final exchange</x:v>
+      </x:c>
+      <x:c r="D105" t="str">
+        <x:v>p-s3-14</x:v>
+      </x:c>
+      <x:c r="E105" t="str">
+        <x:v>encouraging</x:v>
+      </x:c>
+      <x:c r="F105" t="str">
+        <x:v>That is the point. The gradebook summarizes performance. The submission and rubric show what the score can actually support.</x:v>
+      </x:c>
+      <x:c r="G105" t="str">
+        <x:v>p-s3-14.mp3</x:v>
+      </x:c>
+      <x:c r="H105" t="str">
+        <x:v>assets/audio/voice/professor-pixel/scenario-03/p-s3-14.mp3</x:v>
+      </x:c>
+      <x:c r="I105" t="str">
+        <x:v>Draft, Do Not Record</x:v>
+      </x:c>
+      <x:c r="J105" t="str">
+        <x:v>High</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="I2:I48">
     <x:cfRule type="expression" dxfId="13" priority="1">
@@ -2886,7 +4038,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4dd1a4efc35e4c2a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c166f92779b4279"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3061,7 +4213,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cce150aefae4896"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re51967a2d7cb43ba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3269,7 +4421,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf5c945c3c4d4938"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra075f6006df1429a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/asset-management/PromptCraft_Voice_Recording_Tracker.xlsx
+++ b/docs/asset-management/PromptCraft_Voice_Recording_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S1 Record" sheetId="1" r:id="R74b8708b1c8747fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S1 On Screen" sheetId="2" r:id="R3f62be4326e74df4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Existing Audio" sheetId="3" r:id="R42922e1c93a643f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Later Recording" sheetId="4" r:id="R40d3b2b549154795"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retired Names" sheetId="5" r:id="R15d0a2c2f9b74ed5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S1 Record" sheetId="1" r:id="Rcfcb0d85535b4460"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S1 On Screen" sheetId="2" r:id="R1b5bc1245ada4cd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Existing Audio" sheetId="3" r:id="R113ee75bb0064945"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Later Recording" sheetId="4" r:id="Rce6242e5a9ab45c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retired Names" sheetId="5" r:id="Rfef7dfe1f00c42c8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -377,11 +377,35 @@
       <x:c r="A2" s="1" t="str">
         <x:v>Scenario 1 recording queue</x:v>
       </x:c>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
       <x:c r="A3" s="2" t="str">
-        <x:v>Approve the exact wording, then record and check one file per row.</x:v>
-      </x:c>
+        <x:v>Approve the exact wording, then record one file per row using speaker, scenario, and line number.</x:v>
+      </x:c>
+      <x:c r="B3"/>
+      <x:c r="C3"/>
+      <x:c r="D3"/>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4"/>
+      <x:c r="B4"/>
+      <x:c r="C4"/>
+      <x:c r="D4"/>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -432,7 +456,7 @@
         <x:v>The module has five activities, but the names do not tell me much. I keep opening things just to figure out what they are.</x:v>
       </x:c>
       <x:c r="H6" s="7" t="str">
-        <x:v>assets/audio/voice/students/maya/scenario-01/s1-maya-m01.mp3</x:v>
+        <x:v>assets/audio/voice/students/maya/scenario-01/maya_s01_01.mp3</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="55" customHeight="1">
@@ -458,7 +482,7 @@
         <x:v>This is much easier to follow. I can see the path before I start clicking, and the titles tell me what each activity is for.</x:v>
       </x:c>
       <x:c r="H7" s="7" t="str">
-        <x:v>assets/audio/voice/students/maya/scenario-01/s1-maya-m02.mp3</x:v>
+        <x:v>assets/audio/voice/students/maya/scenario-01/maya_s01_02.mp3</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="55" customHeight="1">
@@ -484,7 +508,7 @@
         <x:v>The clearer names and headers helped me find my way. They did not change what the activities actually ask me to demonstrate.</x:v>
       </x:c>
       <x:c r="H8" s="7" t="str">
-        <x:v>assets/audio/voice/students/maya/scenario-01/s1-maya-m03.mp3</x:v>
+        <x:v>assets/audio/voice/students/maya/scenario-01/maya_s01_03.mp3</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="55" customHeight="1">
@@ -510,7 +534,7 @@
         <x:v>Maya has a Canvas module to work through. Start by seeing exactly what she sees before you decide what needs fixing.</x:v>
       </x:c>
       <x:c r="H9" s="7" t="str">
-        <x:v>assets/audio/voice/professor-pixel/scenario-01/s1-professor-pixel-p01.mp3</x:v>
+        <x:v>assets/audio/voice/professor-pixel/scenario-01/pp_s01_01.mp3</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="55" customHeight="1">
@@ -536,7 +560,7 @@
         <x:v>Open all five. Pay attention to what each activity asks Maya to do. We will improve the module only after you understand the current experience.</x:v>
       </x:c>
       <x:c r="H10" s="7" t="str">
-        <x:v>assets/audio/voice/professor-pixel/scenario-01/s1-professor-pixel-p02.mp3</x:v>
+        <x:v>assets/audio/voice/professor-pixel/scenario-01/pp_s01_02.mp3</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="55" customHeight="1">
@@ -562,7 +586,7 @@
         <x:v>Good. You repaired the navigation problem. Now compare what Maya actually does with what the instructor says she should be able to do.</x:v>
       </x:c>
       <x:c r="H11" s="7" t="str">
-        <x:v>assets/audio/voice/professor-pixel/scenario-01/s1-professor-pixel-p03.mp3</x:v>
+        <x:v>assets/audio/voice/professor-pixel/scenario-01/pp_s01_03.mp3</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="55" customHeight="1">
@@ -588,7 +612,7 @@
         <x:v>Exactly. Now apply the same inspection to one of your own modules. We will build the overview in small pieces before Babbage reviews anything.</x:v>
       </x:c>
       <x:c r="H12" s="7" t="str">
-        <x:v>assets/audio/voice/professor-pixel/scenario-01/s1-professor-pixel-p04.mp3</x:v>
+        <x:v>assets/audio/voice/professor-pixel/scenario-01/pp_s01_04.mp3</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="55" customHeight="1">
@@ -614,7 +638,7 @@
         <x:v>You now have a guide you can reuse: make the module path visible, start with the intended learning, and inspect the evidence students actually produce.</x:v>
       </x:c>
       <x:c r="H13" s="7" t="str">
-        <x:v>assets/audio/voice/professor-pixel/scenario-01/s1-professor-pixel-p05.mp3</x:v>
+        <x:v>assets/audio/voice/professor-pixel/scenario-01/pp_s01_05.mp3</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="55" customHeight="1">
@@ -640,7 +664,7 @@
         <x:v>Next comes access. A course can be logically organized and still create barriers for students. That is why the next scenario asks you to examine who can actually use the learning experience you designed.</x:v>
       </x:c>
       <x:c r="H14" s="7" t="str">
-        <x:v>assets/audio/voice/professor-pixel/scenario-01/s1-professor-pixel-p06.mp3</x:v>
+        <x:v>assets/audio/voice/professor-pixel/scenario-01/pp_s01_06.mp3</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -657,7 +681,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bf6c24386f645eb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4264b88169a94ed0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -678,11 +702,29 @@
       <x:c r="A2" s="1" t="str">
         <x:v>Scenario 1 on screen text</x:v>
       </x:c>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
       <x:c r="A3" s="2" t="str">
         <x:v>These Maya quotes are not in the recording queue. Resolve dynamic placeholders before any voice work.</x:v>
       </x:c>
+      <x:c r="B3"/>
+      <x:c r="C3"/>
+      <x:c r="D3"/>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4"/>
+      <x:c r="B4"/>
+      <x:c r="C4"/>
+      <x:c r="D4"/>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -1032,7 +1074,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R252d8b57461e49a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8e681f699a6433f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1053,11 +1095,29 @@
       <x:c r="A2" s="1" t="str">
         <x:v>Existing audio files</x:v>
       </x:c>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
       <x:c r="A3" s="2" t="str">
         <x:v>Files already present in the project; these are not proof that current S1 wording is approved.</x:v>
       </x:c>
+      <x:c r="B3"/>
+      <x:c r="C3"/>
+      <x:c r="D3"/>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4"/>
+      <x:c r="B4"/>
+      <x:c r="C4"/>
+      <x:c r="D4"/>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -1081,7 +1141,7 @@
     </x:row>
     <x:row r="6" ht="27" customHeight="1">
       <x:c r="A6" s="7" t="str">
-        <x:v>background.mp3</x:v>
+        <x:v>music_01_background.mp3</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
         <x:v>Music</x:v>
@@ -1090,7 +1150,7 @@
         <x:v>Application audio</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>assets/audio/music/background.mp3</x:v>
+        <x:v>assets/audio/music/music_01_background.mp3</x:v>
       </x:c>
       <x:c r="E6" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -1101,7 +1161,7 @@
     </x:row>
     <x:row r="7" ht="27" customHeight="1">
       <x:c r="A7" s="7" t="str">
-        <x:v>all-complete.mp3</x:v>
+        <x:v>pp_end_02.mp3</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
         <x:v>Professor Pixel</x:v>
@@ -1110,7 +1170,7 @@
         <x:v>Application audio</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
-        <x:v>assets/audio/voice/professor-pixel/completion/all-complete.mp3</x:v>
+        <x:v>assets/audio/voice/professor-pixel/completion/pp_end_02.mp3</x:v>
       </x:c>
       <x:c r="E7" s="7" t="str">
         <x:v>Planned file present</x:v>
@@ -1121,7 +1181,7 @@
     </x:row>
     <x:row r="8" ht="27" customHeight="1">
       <x:c r="A8" s="7" t="str">
-        <x:v>scenario-complete.mp3</x:v>
+        <x:v>pp_end_01.mp3</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
         <x:v>Professor Pixel</x:v>
@@ -1130,7 +1190,7 @@
         <x:v>Application audio</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
-        <x:v>assets/audio/voice/professor-pixel/completion/scenario-complete.mp3</x:v>
+        <x:v>assets/audio/voice/professor-pixel/completion/pp_end_01.mp3</x:v>
       </x:c>
       <x:c r="E8" s="7" t="str">
         <x:v>Planned file present</x:v>
@@ -1141,7 +1201,7 @@
     </x:row>
     <x:row r="9" ht="27" customHeight="1">
       <x:c r="A9" s="7" t="str">
-        <x:v>decent.mp3</x:v>
+        <x:v>pp_fb_02.mp3</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
         <x:v>Professor Pixel</x:v>
@@ -1150,7 +1210,7 @@
         <x:v>Application audio</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
-        <x:v>assets/audio/voice/professor-pixel/feedback/decent.mp3</x:v>
+        <x:v>assets/audio/voice/professor-pixel/feedback/pp_fb_02.mp3</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
         <x:v>Planned file present</x:v>
@@ -1161,7 +1221,7 @@
     </x:row>
     <x:row r="10" ht="27" customHeight="1">
       <x:c r="A10" s="7" t="str">
-        <x:v>strong.mp3</x:v>
+        <x:v>pp_fb_03.mp3</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
         <x:v>Professor Pixel</x:v>
@@ -1170,7 +1230,7 @@
         <x:v>Application audio</x:v>
       </x:c>
       <x:c r="D10" s="7" t="str">
-        <x:v>assets/audio/voice/professor-pixel/feedback/strong.mp3</x:v>
+        <x:v>assets/audio/voice/professor-pixel/feedback/pp_fb_03.mp3</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
         <x:v>Planned file present</x:v>
@@ -1181,7 +1241,7 @@
     </x:row>
     <x:row r="11" ht="27" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>vague.mp3</x:v>
+        <x:v>pp_fb_01.mp3</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
         <x:v>Professor Pixel</x:v>
@@ -1190,7 +1250,7 @@
         <x:v>Application audio</x:v>
       </x:c>
       <x:c r="D11" s="7" t="str">
-        <x:v>assets/audio/voice/professor-pixel/feedback/vague.mp3</x:v>
+        <x:v>assets/audio/voice/professor-pixel/feedback/pp_fb_01.mp3</x:v>
       </x:c>
       <x:c r="E11" s="7" t="str">
         <x:v>Planned file present</x:v>
@@ -1201,7 +1261,7 @@
     </x:row>
     <x:row r="12" ht="27" customHeight="1">
       <x:c r="A12" s="7" t="str">
-        <x:v>open.mp3</x:v>
+        <x:v>pp_ref_01.mp3</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
         <x:v>Professor Pixel</x:v>
@@ -1210,7 +1270,7 @@
         <x:v>Application audio</x:v>
       </x:c>
       <x:c r="D12" s="7" t="str">
-        <x:v>assets/audio/voice/professor-pixel/reflection/open.mp3</x:v>
+        <x:v>assets/audio/voice/professor-pixel/reflection/pp_ref_01.mp3</x:v>
       </x:c>
       <x:c r="E12" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -1221,27 +1281,27 @@
     </x:row>
     <x:row r="13" ht="27" customHeight="1">
       <x:c r="A13" s="7" t="str">
-        <x:v>intro.mp3</x:v>
+        <x:v>pp_s01_00.mp3</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
         <x:v>Professor Pixel</x:v>
       </x:c>
       <x:c r="C13" s="7" t="str">
-        <x:v>Application audio</x:v>
+        <x:v>Earlier S1 runtime audio</x:v>
       </x:c>
       <x:c r="D13" s="7" t="str">
-        <x:v>assets/audio/voice/professor-pixel/scenario-01/intro.mp3</x:v>
+        <x:v>assets/audio/voice/professor-pixel/scenario-01/pp_s01_00.mp3</x:v>
       </x:c>
       <x:c r="E13" s="7" t="str">
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="F13" s="7" t="str">
-        <x:v>Verify wording before enabling voice playback.</x:v>
+        <x:v>Reserved existing file. New S1 recording lines begin at 01.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="27" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>welcome.mp3</x:v>
+        <x:v>pp_sys_01.mp3</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
         <x:v>Professor Pixel</x:v>
@@ -1250,7 +1310,7 @@
         <x:v>Application audio</x:v>
       </x:c>
       <x:c r="D14" s="7" t="str">
-        <x:v>assets/audio/voice/professor-pixel/system/welcome.mp3</x:v>
+        <x:v>assets/audio/voice/professor-pixel/system/pp_sys_01.mp3</x:v>
       </x:c>
       <x:c r="E14" s="7" t="str">
         <x:v>Planned file present</x:v>
@@ -1262,7 +1322,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1be48fbf05c4536"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra75fdfbfc2e640f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1283,11 +1343,29 @@
       <x:c r="A2" s="1" t="str">
         <x:v>Recording after Scenario 1</x:v>
       </x:c>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
       <x:c r="A3" s="2" t="str">
         <x:v>Keep these decisions separate from the current S1 production queue.</x:v>
       </x:c>
+      <x:c r="B3"/>
+      <x:c r="C3"/>
+      <x:c r="D3"/>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4"/>
+      <x:c r="B4"/>
+      <x:c r="C4"/>
+      <x:c r="D4"/>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -1352,7 +1430,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8b50d7dcd2047c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R190a3fd8bd774e00"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1369,11 +1447,17 @@
       <x:c r="A2" s="1" t="str">
         <x:v>Retired audio names</x:v>
       </x:c>
+      <x:c r="B2"/>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
       <x:c r="A3" s="2" t="str">
         <x:v>Do not assign these names to new recordings.</x:v>
       </x:c>
+      <x:c r="B3"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4"/>
+      <x:c r="B4"/>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -1388,7 +1472,7 @@
         <x:v>s4-interrupt.mp3</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>Retired by asset manifest v150; preserve only as historical reference.</x:v>
+        <x:v>Retired by asset manifest v151; preserve only as historical reference.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="27" customHeight="1">
@@ -1396,7 +1480,7 @@
         <x:v>s4-reveal.mp3</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>Retired by asset manifest v150; preserve only as historical reference.</x:v>
+        <x:v>Retired by asset manifest v151; preserve only as historical reference.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="27" customHeight="1">
@@ -1404,7 +1488,7 @@
         <x:v>s7-closing.mp3</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>Retired by asset manifest v150; preserve only as historical reference.</x:v>
+        <x:v>Retired by asset manifest v151; preserve only as historical reference.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="27" customHeight="1">
@@ -1412,7 +1496,7 @@
         <x:v>scenario-2-intro.mp3</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
-        <x:v>Retired by asset manifest v150; preserve only as historical reference.</x:v>
+        <x:v>Retired by asset manifest v151; preserve only as historical reference.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="27" customHeight="1">
@@ -1420,7 +1504,7 @@
         <x:v>scenario-3-intro.mp3</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Retired by asset manifest v150; preserve only as historical reference.</x:v>
+        <x:v>Retired by asset manifest v151; preserve only as historical reference.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="27" customHeight="1">
@@ -1428,7 +1512,7 @@
         <x:v>scenario-4-intro.mp3</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>Retired by asset manifest v150; preserve only as historical reference.</x:v>
+        <x:v>Retired by asset manifest v151; preserve only as historical reference.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="27" customHeight="1">
@@ -1436,7 +1520,7 @@
         <x:v>scenario-5-intro.mp3</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>Retired by asset manifest v150; preserve only as historical reference.</x:v>
+        <x:v>Retired by asset manifest v151; preserve only as historical reference.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="27" customHeight="1">
@@ -1444,7 +1528,7 @@
         <x:v>scenario-6-intro.mp3</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
-        <x:v>Retired by asset manifest v150; preserve only as historical reference.</x:v>
+        <x:v>Retired by asset manifest v151; preserve only as historical reference.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="27" customHeight="1">
@@ -1452,7 +1536,7 @@
         <x:v>scenario-7-intro.mp3</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>Retired by asset manifest v150; preserve only as historical reference.</x:v>
+        <x:v>Retired by asset manifest v151; preserve only as historical reference.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="27" customHeight="1">
@@ -1460,13 +1544,13 @@
         <x:v>scenario-8-intro.mp3</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>Retired by asset manifest v150; preserve only as historical reference.</x:v>
+        <x:v>Retired by asset manifest v151; preserve only as historical reference.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb809d15d1fd4a13"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra28c3e8f814a44f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>